--- a/www/flightdata/xlsx/eoss-365.xlsx
+++ b/www/flightdata/xlsx/eoss-365.xlsx
@@ -3414,7 +3414,7 @@
         <v>27619.45</v>
       </c>
       <c r="I2">
-        <v>671</v>
+        <v>432</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
